--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486978_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486978_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.676</v>
+        <v>8.180899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1562</v>
+        <v>6.6018</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5198</v>
+        <v>1.5791</v>
       </c>
       <c r="G2" t="n">
         <v>5.9499</v>
@@ -610,13 +610,13 @@
         <v>2.4641</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4525</v>
+        <v>0.0524</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6705</v>
+        <v>-0.225</v>
       </c>
       <c r="U2" t="n">
-        <v>0.218</v>
+        <v>0.2773</v>
       </c>
       <c r="V2" t="n">
         <v>1.7679</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1971</v>
+        <v>6.1887</v>
       </c>
       <c r="E3" t="n">
-        <v>1.931</v>
+        <v>2.8337</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2661</v>
+        <v>3.355</v>
       </c>
       <c r="G3" t="n">
         <v>2.629</v>
@@ -688,13 +688,13 @@
         <v>1.6427</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.514</v>
+        <v>0.4776</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9804</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4663</v>
+        <v>0.5552</v>
       </c>
       <c r="V3" t="n">
         <v>2.4661</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SANTANA LUCHORO</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8108</v>
+        <v>0.8194</v>
       </c>
       <c r="E4" t="n">
-        <v>1.1101</v>
+        <v>-0.3425</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7007</v>
+        <v>1.1619</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1925</v>
+        <v>0.7138</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4922</v>
+        <v>1.3686</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.2997</v>
+        <v>-0.6548</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1022</v>
+        <v>1.2074</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0103</v>
+        <v>1.1679</v>
       </c>
       <c r="L4" t="n">
-        <v>0.092</v>
+        <v>0.0395</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09030000000000001</v>
+        <v>-0.4936</v>
       </c>
       <c r="N4" t="n">
-        <v>1.482</v>
+        <v>0.2007</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.3917</v>
+        <v>-0.6943</v>
       </c>
       <c r="P4" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0534</v>
+        <v>-1.0267</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2588</v>
+        <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>2.5915</v>
+        <v>-0.3399</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8827</v>
+        <v>-0.7634</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7089</v>
+        <v>0.4235</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="W4" t="n">
-        <v>1.1786</v>
+        <v>0.2402</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. SANTANA LUCHORO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.111</v>
+        <v>0.3612</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1992</v>
+        <v>-0.0134</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3101</v>
+        <v>0.3747</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7138</v>
+        <v>0.1925</v>
       </c>
       <c r="H5" t="n">
-        <v>1.3686</v>
+        <v>1.4922</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6548</v>
+        <v>-1.2997</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2074</v>
+        <v>0.1022</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1679</v>
+        <v>0.0103</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0395</v>
+        <v>0.092</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4936</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2007</v>
+        <v>1.482</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6943</v>
+        <v>-1.3917</v>
       </c>
       <c r="P5" t="n">
         <v>0.2053</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0484</v>
+        <v>1.142</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6201</v>
+        <v>0.7592</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5717</v>
+        <v>0.3828</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2402</v>
+        <v>-1.1786</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="G6" t="n">
         <v>0.1395</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.475</v>
+        <v>-0.4248</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5523</v>
+        <v>-1.5911</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0774</v>
+        <v>1.1663</v>
       </c>
       <c r="G7" t="n">
         <v>-1.5803</v>
@@ -1000,13 +1000,13 @@
         <v>1.0267</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.6092</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3834</v>
+        <v>0.3447</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1756</v>
+        <v>0.2645</v>
       </c>
       <c r="V7" t="n">
         <v>-0.4805</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.6295</v>
+        <v>-1.6962</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4352</v>
+        <v>-0.2647</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1943</v>
+        <v>-1.4314</v>
       </c>
       <c r="G8" t="n">
         <v>0.3627</v>
@@ -1078,13 +1078,13 @@
         <v>0.8214</v>
       </c>
       <c r="S8" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0233</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.651</v>
+        <v>-0.4805</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7409</v>
+        <v>0.5038</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8768</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>L. FERRANDO ORTELLS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6288</v>
+        <v>-1.7731</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2481</v>
+        <v>-3.4758</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3807</v>
+        <v>1.7027</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.1967</v>
+        <v>0.6947</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0867</v>
+        <v>1.2813</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1101</v>
+        <v>-0.5866</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0111</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.7348</v>
+        <v>-0.0321</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2763</v>
+        <v>-0.6579</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1856</v>
+        <v>1.3847</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6482</v>
+        <v>1.3134</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8338</v>
+        <v>0.0713</v>
       </c>
       <c r="P9" t="n">
-        <v>1.2321</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0341</v>
+        <v>0.1482</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2826</v>
+        <v>0.0541</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2485</v>
+        <v>0.0941</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W9" t="n">
-        <v>0.4805</v>
+        <v>0.2402</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. FERRANDO ORTELLS</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8833</v>
+        <v>-2.8488</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3785</v>
+        <v>-2.7052</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4952</v>
+        <v>-0.1436</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6947</v>
+        <v>-3.1967</v>
       </c>
       <c r="H10" t="n">
-        <v>1.2813</v>
+        <v>-1.0867</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5866</v>
+        <v>-2.1101</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.0111</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0321</v>
+        <v>-1.7348</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6579</v>
+        <v>-1.2763</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3847</v>
+        <v>-0.1856</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3134</v>
+        <v>0.6482</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0713</v>
+        <v>-0.8338</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.4374</v>
+        <v>1.2321</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6427</v>
+        <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.962</v>
+        <v>-0.1859</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8486</v>
+        <v>-0.1745</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1134</v>
+        <v>-0.0114</v>
       </c>
       <c r="V10" t="n">
+        <v>-0.6982</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.4805</v>
+      </c>
+      <c r="X10" t="n">
         <v>-1.1786</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0.2402</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-1.4189</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.3375</v>
+        <v>8.996199999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3839999999999995</v>
+        <v>1.042799999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>7.9535</v>
+        <v>7.953600000000001</v>
       </c>
       <c r="G11" t="n">
         <v>5.905100000000001</v>
@@ -1285,7 +1285,7 @@
         <v>-9.406600000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>5.476800000000001</v>
+        <v>5.4768</v>
       </c>
       <c r="K11" t="n">
         <v>8.859999999999999</v>
@@ -1294,7 +1294,7 @@
         <v>-3.3831</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4282999999999999</v>
+        <v>0.4283</v>
       </c>
       <c r="N11" t="n">
         <v>6.4518</v>
@@ -1312,22 +1312,22 @@
         <v>12.3206</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3174</v>
+        <v>1.9763</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2219</v>
+        <v>-0.5630999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5393</v>
+        <v>2.5392</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9385000000000006</v>
+        <v>-0.9385000000000004</v>
       </c>
       <c r="W11" t="n">
         <v>6.396</v>
       </c>
       <c r="X11" t="n">
-        <v>-7.3346</v>
+        <v>-7.334600000000001</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.5699</v>
+        <v>3.6055</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4485</v>
+        <v>2.2853</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1215</v>
+        <v>1.3202</v>
       </c>
       <c r="G12" t="n">
         <v>0.9402</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0026</v>
+        <v>0.0329</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9804</v>
+        <v>-0.1435</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0223</v>
+        <v>0.1765</v>
       </c>
       <c r="V12" t="n">
         <v>2.8377</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. FERRER IGLESIA</t>
+          <t>E. KALU</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6181</v>
+        <v>0.3151</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7966</v>
+        <v>-0.4066</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1785</v>
+        <v>0.7217</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.7672</v>
+        <v>-2.1555</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.2067</v>
+        <v>-1.9532</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5606</v>
+        <v>-0.2023</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.1257</v>
+        <v>0.3375</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.4019</v>
+        <v>0.1007</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7238</v>
+        <v>0.2368</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6415</v>
+        <v>-2.4931</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8047</v>
+        <v>-2.054</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1632</v>
+        <v>-0.4391</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8214</v>
+        <v>1.8481</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8042</v>
+        <v>0.1297</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7437</v>
+        <v>-0.5387999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.0605</v>
+        <v>0.6685</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4189</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. CASTILLO CARRASCO</t>
+          <t>N. FERRER IGLESIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.2461</v>
+        <v>-0.081</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2899</v>
+        <v>0.4828</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0438</v>
+        <v>-0.5638</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2418</v>
+        <v>-1.7672</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1656</v>
+        <v>-1.2067</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.5606</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0395</v>
+        <v>-1.1257</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.4019</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0395</v>
+        <v>-0.7238</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2813</v>
+        <v>-0.6415</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1656</v>
+        <v>-0.8047</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1157</v>
+        <v>0.1632</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1131</v>
+        <v>1.1051</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3294</v>
+        <v>0.4299</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2162</v>
+        <v>0.6752</v>
       </c>
       <c r="V14" t="n">
-        <v>0.1088</v>
+        <v>-0.2402</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1088</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. TOMAIC TOMAIC</t>
+          <t>J. CASTILLO CARRASCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.7911</v>
+        <v>-0.1659</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4223</v>
+        <v>-0.2899</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3688</v>
+        <v>0.124</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.1048</v>
+        <v>-0.2418</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.0914</v>
+        <v>-0.1656</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9866</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2562</v>
+        <v>0.0395</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.4268</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1706</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8486</v>
+        <v>-0.2813</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6646</v>
+        <v>-0.1656</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1839</v>
+        <v>-0.1157</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.616</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.2588</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6427</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.17</v>
+        <v>-0.0329</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9141</v>
+        <v>-0.3294</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2559</v>
+        <v>0.2964</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2402</v>
+        <v>0.1088</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4189</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. KALU</t>
+          <t>F. GARRIDO TEBAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9367</v>
+        <v>-0.5164</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2434</v>
+        <v>-0.7075</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3067</v>
+        <v>0.1911</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.1555</v>
+        <v>1.3945</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9532</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.2023</v>
+        <v>1.9656</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3375</v>
+        <v>0.052</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1007</v>
+        <v>-0.6584</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2368</v>
+        <v>0.7104</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.4931</v>
+        <v>1.3425</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.054</v>
+        <v>0.0873</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4391</v>
+        <v>1.2552</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6427</v>
+        <v>0.2053</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1221</v>
+        <v>-0.9376</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.3756</v>
+        <v>-0.5541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2535</v>
+        <v>-0.3834</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9782</v>
+        <v>-0.7009</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9648</v>
+        <v>-1.174</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0134</v>
+        <v>0.473</v>
       </c>
       <c r="G17" t="n">
         <v>0.5457</v>
@@ -1780,13 +1780,13 @@
         <v>0.616</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6676</v>
+        <v>-0.3904</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2249</v>
+        <v>-0.4341</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4427</v>
+        <v>0.0437</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2402</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. GARRIDO TEBAN</t>
+          <t>J. TOMAIC TOMAIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0185</v>
+        <v>-1.6855</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8121</v>
+        <v>-1.0499</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2064</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3945</v>
+        <v>-2.1048</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5711000000000001</v>
+        <v>-3.0914</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9656</v>
+        <v>0.9866</v>
       </c>
       <c r="J18" t="n">
-        <v>0.052</v>
+        <v>-0.2562</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6584</v>
+        <v>-1.4268</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7104</v>
+        <v>1.1706</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3425</v>
+        <v>-1.8486</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0873</v>
+        <v>-1.6646</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2552</v>
+        <v>-0.1839</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-2.2588</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4107</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4397</v>
+        <v>1.2756</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6587</v>
+        <v>0.2865</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.781</v>
+        <v>0.9891</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1786</v>
+        <v>-0.2402</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1786</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.3078</v>
+        <v>-2.2806</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5444</v>
+        <v>-1.3813</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7633</v>
+        <v>-0.8994</v>
       </c>
       <c r="G19" t="n">
         <v>0.9774</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8586</v>
+        <v>-0.1143</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8677</v>
+        <v>0.0309</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0091</v>
+        <v>-0.1452</v>
       </c>
       <c r="V19" t="n">
         <v>-2.117</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8189</v>
+        <v>-2.3063</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.8436</v>
+        <v>-2.5298</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0247</v>
+        <v>0.2235</v>
       </c>
       <c r="G20" t="n">
         <v>1.8063</v>
@@ -2014,13 +2014,13 @@
         <v>1.4374</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7504</v>
+        <v>-1.2378</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5151</v>
+        <v>-1.2012</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2354</v>
+        <v>-0.0366</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4284</v>
+        <v>-3.1268</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.0782</v>
+        <v>-3.1828</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3503</v>
+        <v>0.056</v>
       </c>
       <c r="G21" t="n">
         <v>-5.2998</v>
@@ -2092,13 +2092,13 @@
         <v>2.0534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0547</v>
+        <v>0.2469</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0191</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0738</v>
+        <v>0.3324</v>
       </c>
       <c r="V21" t="n">
         <v>1.31</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-8.337699999999998</v>
+        <v>-6.942799999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.953600000000001</v>
+        <v>-7.9537</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3840000000000002</v>
+        <v>1.0107</v>
       </c>
       <c r="G22" t="n">
         <v>-5.905</v>
@@ -2143,16 +2143,16 @@
         <v>9.406499999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4281000000000001</v>
+        <v>-0.4280999999999997</v>
       </c>
       <c r="K22" t="n">
         <v>-6.4516</v>
       </c>
       <c r="L22" t="n">
-        <v>6.023500000000001</v>
+        <v>6.0235</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.476900000000001</v>
+        <v>-5.4769</v>
       </c>
       <c r="N22" t="n">
         <v>-8.860199999999999</v>
@@ -2170,13 +2170,13 @@
         <v>10.2671</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3174</v>
+        <v>0.07720000000000005</v>
       </c>
       <c r="T22" t="n">
-        <v>-2.5395</v>
+        <v>-2.5393</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2218</v>
+        <v>2.6166</v>
       </c>
       <c r="V22" t="n">
         <v>0.9384999999999994</v>
@@ -2185,7 +2185,7 @@
         <v>7.3344</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.396199999999999</v>
+        <v>-6.3962</v>
       </c>
     </row>
   </sheetData>
